--- a/stories/arbres/ATOM-EMO.LEX.007-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jocelyn attend avec maman. Ses jambes bougent. Ses mains froissent le manteau. Maman dit : tu es nerveux. Le corps n'arrive pas à tenir. On peut demander une pause. Jocelyn dit : je suis nerveux. Je veux une pause. Maman l'écoute. Ils s'assoient près de la fenêtre. Jocelyn souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
+          <t>Jocelyn attend avec maman. Ses jambes bougent. Ses mains froissent le manteau. Tu es nerveux. Le corps n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Maman l'écoute. Ils s'assoient près de la fenêtre. Jocelyn souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jocelyn attend avec maman. Ses jambes bougent. Ses mains froissent le manteau.
+maman|Tu es nerveux.
+narrateur|Le corps n'arrive pas à tenir. On peut demander une pause.
+enfant-m|Je suis nerveux. Je veux une pause. Maman l'écoute.
+narrateur|Ils s'assoient près de la fenêtre. Jocelyn souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1492,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Jocelyn n'arrive pas à tenir. Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1521,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jocelyn a dit : je suis nerveux. Il a demandé une pause.</t>
+          <t>Jocelyn Je suis nerveux. Il a demandé une pause.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1663,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jocelyn
+enfant-f|Je suis nerveux. Il a demandé une pause.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman donne la main. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Ils s'assoient près de la fenêtre. Jocelyn souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Jocelyn n'arrive pas à tenir. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
 enfant-f|Je suis nerveux. Il a demandé une pause.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Maman donne la main. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.007-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jocelyn est nerveux et demande une pause</t>
+          <t>Aniss est nerveux et demande une pause</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss regarde les poissons. Son corps n'arrive pas à tenir. Il dit qu'il est nerveux. Il demande une pause.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jocelyn attend avec maman. Ses jambes bougent. Ses mains froissent le manteau. Tu es nerveux. Le corps n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Maman l'écoute. Ils s'assoient près de la fenêtre. Jocelyn souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
+          <t>Dans le bocal, les bulles montent, une par une. Un poisson orange passe derrière une plante verte. Le verre du bocal est un peu froid. Une chaise jaune attend contre le mur. Des manteaux d'hiver pendent à un crochet. Un gant rouge a glissé par terre. Le sable du fond du bocal est tout fin. Une plante plastique danse un peu. Je ramasse le gant, Aniss. Il était sous la chaise jaune. Le poisson est tout orange. Oui. Il nage tout doux. En ce moment, Aniss attend avec maman. Ses jambes bougent sur la chaise jaune. Ses mains froissent le manteau trop chaud. Tu es nerveux, Aniss. Je vois ton corps qui n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Je t'écoute. Viens. On s'assoit près de la fenêtre. Ils s'assoient près de la fenêtre. Un peu de lumière tombe sur les genoux d'Aniss. Souffle une fois, comme une bulle. Aniss souffle. Il s'assoit bien. Ses mains se posent sur ses genoux. La pause aide. Nerveux, ce n'est pas vilain. Je me pose. Bravo, Aniss. C'est du bon travail. Tes jambes sont plus calmes ? Oui. Comme le poisson. Le poisson nage. Toi, tu t'assois. Une bulle arrive en haut du bocal. Elle éclate, tout petit. On regarde encore une bulle, ensemble ? Oui. Tout doux. Le gant rouge est revenu dans la poche. Tu as demandé une pause. Parce que j'étais nerveux. Et nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jocelyn attend avec maman. Ses jambes bougent. Ses mains froissent le manteau.
-maman|Tu es nerveux.
-narrateur|Le corps n'arrive pas à tenir. On peut demander une pause.
-enfant-m|Je suis nerveux. Je veux une pause. Maman l'écoute.
-narrateur|Ils s'assoient près de la fenêtre. Jocelyn souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.</t>
+          <t>narrateur|Dans le bocal, les bulles montent, une par une.
+narrateur|Un poisson orange passe derrière une plante verte.
+narrateur|Le verre du bocal est un peu froid.
+narrateur|Une chaise jaune attend contre le mur.
+narrateur|Des manteaux d'hiver pendent à un crochet.
+narrateur|Un gant rouge a glissé par terre.
+narrateur|Le sable du fond du bocal est tout fin.
+narrateur|Une plante plastique danse un peu.
+maman|Je ramasse le gant, Aniss.
+maman|Il était sous la chaise jaune.
+enfant-m|Le poisson est tout orange.
+maman|Oui.
+maman|Il nage tout doux.
+narrateur|En ce moment, Aniss attend avec maman.
+narrateur|Ses jambes bougent sur la chaise jaune.
+narrateur|Ses mains froissent le manteau trop chaud.
+maman|Tu es nerveux, Aniss.
+maman|Je vois ton corps qui n'arrive pas à tenir.
+maman|On peut demander une pause.
+enfant-m|Je suis nerveux.
+enfant-m|Je veux une pause.
+maman|Je t'écoute.
+maman|Viens.
+maman|On s'assoit près de la fenêtre.
+narrateur|Ils s'assoient près de la fenêtre.
+narrateur|Un peu de lumière tombe sur les genoux d'Aniss.
+maman|Souffle une fois, comme une bulle.
+narrateur|Aniss souffle.
+narrateur|Il s'assoit bien.
+narrateur|Ses mains se posent sur ses genoux.
+maman|La pause aide.
+maman|Nerveux, ce n'est pas vilain.
+enfant-m|Je me pose.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+maman|Tes jambes sont plus calmes ?
+enfant-m|Oui.
+enfant-m|Comme le poisson.
+maman|Le poisson nage.
+maman|Toi, tu t'assois.
+narrateur|Une bulle arrive en haut du bocal.
+narrateur|Elle éclate, tout petit.
+maman|On regarde encore une bulle, ensemble ?
+enfant-m|Oui.
+enfant-m|Tout doux.
+narrateur|Le gant rouge est revenu dans la poche.
+maman|Tu as demandé une pause.
+enfant-m|Parce que j'étais nerveux.
+maman|Et nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jocelyn n'arrive pas à tenir. Que fait-il ?</t>
+          <t>Aniss n'arrive pas à tenir. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1556,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Jocelyn n'arrive pas à tenir. Que fait-il ?</t>
+          <t>narrateur|Aniss n'arrive pas à tenir.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jocelyn Je suis nerveux. Il a demandé une pause.</t>
+          <t>Aniss a nommé : nerveux. Il a demandé une pause. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis près de la fenêtre. Bravo. C'est du bon travail. Le poisson orange passe encore une fois. Nerveux, ce n'est pas vilain. Une pause, c'est un bon geste. Je souffle encore une fois. Comme une bulle. C'est bien. La plante plastique danse encore un peu. On reste près de la fenêtre ? Oui. Les bulles montent.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,8 +1729,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jocelyn
-enfant-f|Je suis nerveux. Il a demandé une pause.</t>
+          <t>narrateur|Aniss a nommé : nerveux.
+narrateur|Il a demandé une pause.
+enfant-m|Je suis nerveux.
+enfant-m|Je veux une pause.
+maman|Oui.
+maman|Tu t'es assis près de la fenêtre.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Le poisson orange passe encore une fois.
+maman|Nerveux, ce n'est pas vilain.
+maman|Une pause, c'est un bon geste.
+enfant-m|Je souffle encore une fois.
+maman|Comme une bulle.
+maman|C'est bien.
+narrateur|La plante plastique danse encore un peu.
+maman|On reste près de la fenêtre ?
+enfant-m|Oui.
+enfant-m|Les bulles montent.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1774,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman donne la main. Ils rentrent.</t>
+          <t>Maman tend la main. Tu prends ma main, Aniss ? Oui, maman. On rentre. Le manteau est moins chaud. Ils passent devant le bocal. Au revoir, poisson. Tu as demandé une pause. C'est du bon travail. La chaise jaune reste contre le mur. Une bulle monte encore, toute seule. Je suis moins nerveux. On marche tout doux, maintenant. Le gant rouge reste dans la poche.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1914,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman donne la main. Ils rentrent.</t>
+          <t>narrateur|Maman tend la main.
+maman|Tu prends ma main, Aniss ?
+enfant-m|Oui, maman.
+maman|On rentre.
+maman|Le manteau est moins chaud.
+narrateur|Ils passent devant le bocal.
+enfant-m|Au revoir, poisson.
+maman|Tu as demandé une pause.
+maman|C'est du bon travail.
+narrateur|La chaise jaune reste contre le mur.
+narrateur|Une bulle monte encore, toute seule.
+enfant-m|Je suis moins nerveux.
+maman|On marche tout doux, maintenant.
+narrateur|Le gant rouge reste dans la poche.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Aniss. Tu as fait du bon travail. Les bulles montent encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2095,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais nerveux.
+enfant-m|J'ai demandé une pause.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Les bulles montent encore.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dans le bocal, les bulles montent, une par une. Un poisson orange passe derrière une plante verte. Le verre du bocal est un peu froid. Une chaise jaune attend contre le mur. Des manteaux d'hiver pendent à un crochet. Un gant rouge a glissé par terre. Le sable du fond du bocal est tout fin. Une plante plastique danse un peu. Je ramasse le gant, Aniss. Il était sous la chaise jaune. Le poisson est tout orange. Oui. Il nage tout doux. En ce moment, Aniss attend avec maman. Ses jambes bougent sur la chaise jaune. Ses mains froissent le manteau trop chaud. Tu es nerveux, Aniss. Je vois ton corps qui n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Je t'écoute. Viens. On s'assoit près de la fenêtre. Ils s'assoient près de la fenêtre. Un peu de lumière tombe sur les genoux d'Aniss. Souffle une fois, comme une bulle. Aniss souffle. Il s'assoit bien. Ses mains se posent sur ses genoux. La pause aide. Nerveux, ce n'est pas vilain. Je me pose. Bravo, Aniss. C'est du bon travail. Tes jambes sont plus calmes ? Oui. Comme le poisson. Le poisson nage. Toi, tu t'assois. Une bulle arrive en haut du bocal. Elle éclate, tout petit. On regarde encore une bulle, ensemble ? Oui. Tout doux. Le gant rouge est revenu dans la poche. Tu as demandé une pause. Parce que j'étais nerveux. Et nerveux, ce n'est pas vilain.</t>
+          <t>Dans le bocal, les bulles montent, une par une. Un poisson orange passe derrière une plante verte. Le verre du bocal est un peu froid. Une chaise jaune attend contre le mur. Des manteaux d'hiver pendent à un crochet. Un gant rouge a glissé par terre. Le sable du fond du bocal est tout fin. Une plante plastique danse un peu. Je ramasse le gant, Aniss. Il était sous la chaise jaune. Le poisson est tout orange. Oui. Il nage tout doux. En ce moment, Aniss attend avec maman. Ses jambes bougent sur la chaise jaune. Ses mains froissent le manteau trop chaud. Tu es nerveux, Aniss. Je vois ton corps qui n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Je t'écoute. Viens. On s'assoit près de la fenêtre. Ils s'assoient près de la fenêtre. Un peu de lumière tombe sur les genoux d'Aniss. Souffle une fois, comme une bulle. Aniss souffle. Il s'assoit bien. Ses mains se posent sur ses genoux. La pause aide. Nerveux, ce n'est pas vilain. Je me pose. Bravo, Aniss. Tes jambes sont plus calmes ? Oui. Comme le poisson. Le poisson nage. Toi, tu t'assois. Une bulle arrive en haut du bocal. Elle éclate, tout petit. On regarde encore une bulle, ensemble ? Oui. Tout doux. Le gant rouge est revenu dans la poche. Tu as demandé une pause. Parce que j'étais nerveux. Et nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jocelyn attend avec maman. Ses jambes bougent. Ses mains froissent le manteau. Maman dit : tu es &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;. Le corps n'arrive pas à tenir. On peut demander une pause. Jocelyn dit : je suis nerveux. Je veux une pause. Maman l'écoute. Ils s'assoient près de la fenêtre. Jocelyn souffle. Il s'assoit. La pause aide. Nerveux, ce n'est pas vilain.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dans le bocal, les bulles montent, une par une. Un poisson orange passe derrière une plante verte. Le verre du bocal est un peu froid. Une chaise jaune attend contre le mur. Des manteaux d'hiver pendent à un crochet. Un gant rouge a glissé par terre. Le sable du fond du bocal est tout fin. Une plante plastique danse un peu. Je ramasse le gant, Aniss. Il était sous la chaise jaune. Le poisson est tout orange. Oui. Il nage tout doux. En ce moment, Aniss attend avec maman. Ses jambes bougent sur la chaise jaune. Ses mains froissent le manteau trop chaud. Tu es nerveux, Aniss. Je vois ton corps qui n'arrive pas à tenir. On peut demander une pause. Je suis nerveux. Je veux une pause. Je t'écoute. Viens. On s'assoit près de la fenêtre. Ils s'assoient près de la fenêtre. Un peu de lumière tombe sur les genoux d'Aniss. Souffle une fois, comme une bulle. Aniss souffle. Il s'assoit bien. Ses mains se posent sur ses genoux. La pause aide. Nerveux, ce n'est pas vilain. Je me pose. Bravo, Aniss. Tes jambes sont plus calmes ? Oui. Comme le poisson. Le poisson nage. Toi, tu t'assois. Une bulle arrive en haut du bocal. Elle éclate, tout petit. On regarde encore une bulle, ensemble ? Oui. Tout doux. Le gant rouge est revenu dans la poche. Tu as demandé une pause. Parce que j'étais nerveux. Et nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1358,7 +1358,6 @@
 maman|Nerveux, ce n'est pas vilain.
 enfant-m|Je me pose.
 maman|Bravo, Aniss.
-maman|C'est du bon travail.
 maman|Tes jambes sont plus calmes ?
 enfant-m|Oui.
 enfant-m|Comme le poisson.
@@ -1375,7 +1374,6 @@
 maman|Et nerveux, ce n'est pas vilain.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1405,7 +1403,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jocelyn n'arrive pas à tenir. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss n'arrive pas à tenir. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1560,7 +1558,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1585,12 +1582,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a nommé : nerveux. Il a demandé une pause. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis près de la fenêtre. Bravo. C'est du bon travail. Le poisson orange passe encore une fois. Nerveux, ce n'est pas vilain. Une pause, c'est un bon geste. Je souffle encore une fois. Comme une bulle. C'est bien. La plante plastique danse encore un peu. On reste près de la fenêtre ? Oui. Les bulles montent.</t>
+          <t>Aniss a nommé : nerveux. Il a demandé une pause. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis près de la fenêtre. Bravo. Le poisson orange passe encore une fois. Nerveux, ce n'est pas vilain. Une pause, c'est un bon geste. Je souffle encore une fois. Comme une bulle. C'est bien. La plante plastique danse encore un peu. On reste près de la fenêtre ? Oui. Les bulles montent.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jocelyn a dit : je suis &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;. Il a demandé une pause.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a nommé : nerveux. Il a demandé une pause. Je suis nerveux. Je veux une pause. Oui. Tu t'es assis près de la fenêtre. Bravo. Le poisson orange passe encore une fois. Nerveux, ce n'est pas vilain. Une pause, c'est un bon geste. Je souffle encore une fois. Comme une bulle. C'est bien. La plante plastique danse encore un peu. On reste près de la fenêtre ? Oui. Les bulles montent.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1736,7 +1733,6 @@
 maman|Oui.
 maman|Tu t'es assis près de la fenêtre.
 maman|Bravo.
-maman|C'est du bon travail.
 narrateur|Le poisson orange passe encore une fois.
 maman|Nerveux, ce n'est pas vilain.
 maman|Une pause, c'est un bon geste.
@@ -1749,7 +1745,6 @@
 enfant-m|Les bulles montent.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1774,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman tend la main. Tu prends ma main, Aniss ? Oui, maman. On rentre. Le manteau est moins chaud. Ils passent devant le bocal. Au revoir, poisson. Tu as demandé une pause. C'est du bon travail. La chaise jaune reste contre le mur. Une bulle monte encore, toute seule. Je suis moins nerveux. On marche tout doux, maintenant. Le gant rouge reste dans la poche.</t>
+          <t>Maman tend la main. Tu prends ma main, Aniss ? Oui, maman. On rentre. Le manteau est moins chaud. Ils passent devant le bocal. Au revoir, poisson. Tu as demandé une pause. La chaise jaune reste contre le mur. Une bulle monte encore, toute seule. Je suis moins nerveux. On marche tout doux, maintenant. Le gant rouge reste dans la poche.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman tend la main. Tu prends ma main, Aniss ? Oui, maman. On rentre. Le manteau est moins chaud. Ils passent devant le bocal. Au revoir, poisson. Tu as demandé une pause. La chaise jaune reste contre le mur. Une bulle monte encore, toute seule. Je suis moins nerveux. On marche tout doux, maintenant. Le gant rouge reste dans la poche.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1922,7 +1917,6 @@
 narrateur|Ils passent devant le bocal.
 enfant-m|Au revoir, poisson.
 maman|Tu as demandé une pause.
-maman|C'est du bon travail.
 narrateur|La chaise jaune reste contre le mur.
 narrateur|Une bulle monte encore, toute seule.
 enfant-m|Je suis moins nerveux.
@@ -1930,7 +1924,6 @@
 narrateur|Le gant rouge reste dans la poche.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1955,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Aniss. Tu as fait du bon travail. Les bulles montent encore. L'histoire est finie.</t>
+          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Aniss. Les bulles montent encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais nerveux. J'ai demandé une pause. Bravo, Aniss. Les bulles montent encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,12 +2091,9 @@
           <t>enfant-m|J'étais nerveux.
 enfant-m|J'ai demandé une pause.
 maman|Bravo, Aniss.
-maman|Tu as fait du bon travail.
-narrateur|Les bulles montent encore.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les bulles montent encore.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2122,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2157,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jocelyn, maman</t>
+          <t>Aniss, maman</t>
         </is>
       </c>
     </row>
